--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2247-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2247-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA493671-BA1D-4E80-BD88-879E76761768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35549639-D1C2-4FC1-98E1-6BDA0AFCD1CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{D4AC897B-EF7E-4BD2-878D-3C68D9EA504B}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{DB8D6F5C-F48C-4A9A-A3AD-1901E63D9C9A}"/>
   </bookViews>
   <sheets>
     <sheet name="2247-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1471,25 +1471,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{661458B5-175F-46F5-BEE5-E81DC1FBB08F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22CFDAA4-1832-427D-83D3-FFD0F1931E0E}">
   <dimension ref="A1:R16"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="7.5" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1517,7 +1517,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1547,7 +1547,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1643,7 +1643,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>4.62</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="39"/>
       <c r="B6" s="40"/>
       <c r="C6" s="42"/>
@@ -1723,7 +1723,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>2.31</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="47">
         <v>2025</v>
       </c>
@@ -1833,7 +1833,7 @@
         <v>5.47</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="49">
         <v>2024</v>
       </c>
@@ -1887,7 +1887,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="47">
         <v>2023</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="49">
         <v>2022</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="47">
         <v>2021</v>
       </c>
@@ -2049,7 +2049,7 @@
         <v>4.8099999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="49">
         <v>2020</v>
       </c>
@@ -2103,7 +2103,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="47">
         <v>2019</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>3.71</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="49">
         <v>2018</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>3.59</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="47" t="s">
         <v>30</v>
       </c>
